--- a/docs/dossiers/dossier-restaurant-a-paris-2f9d751f.xlsx
+++ b/docs/dossiers/dossier-restaurant-a-paris-2f9d751f.xlsx
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>273 360 € Restaurant à Paris (75015) 104 m² Voir l'annonce</t>
+          <t>273 360 € 2 628 €/m² Vente Restaurant 104 m² 104 m² Citroën-Boucicaut, Paris 15ème arrondissement (75015) Voir l'annonce</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-restaurant-a-paris-2f9d751f.xlsx
+++ b/docs/dossiers/dossier-restaurant-a-paris-2f9d751f.xlsx
@@ -841,7 +841,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
